--- a/utilities/onboarding-tool/scripts/stage1-planning/discovery-resource-planning-form-byo-vnet.xlsx
+++ b/utilities/onboarding-tool/scripts/stage1-planning/discovery-resource-planning-form-byo-vnet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\discovery-tool\discovery\utilities\onboarding-tool\scripts\stage1-planning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\discovery\discovery\utilities\onboarding-tool\scripts\stage1-planning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C1905F-B8A6-456D-9E02-06A8754851A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE681F0-7AB7-48AE-8E17-B8150DD4F974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -181,9 +181,6 @@
     <t>byo-existing</t>
   </si>
   <si>
-    <t>byo-existing = your VNet already exists; the tool does NOT build it (Stage 3 validates). Use 'byo' instead to have the tool provision subnets into your VNet. FR1.2</t>
-  </si>
-  <si>
     <t>network.networkResourceGroup</t>
   </si>
   <si>
@@ -319,19 +316,19 @@
     <t>byo</t>
   </si>
   <si>
-    <t>byo | managed. Bookshelf (bookshelf.inScope=true) requires byo with storage.account set.</t>
+    <t>Must be byo. Every Discovery project needs a storage account you own; managed is not supported.</t>
   </si>
   <si>
     <t>storage.account</t>
   </si>
   <si>
-    <t>Name of the storage account you pre-created for project data (required, byo). The tool does not create it; Stage 1 checks that it exists.</t>
+    <t>Required. Name (not resource ID) of an existing StorageV2 account in the target subscription. The tool does not create it. Create one with: az storage account create -g &lt;rg&gt; -n &lt;globally-unique-name&gt; -l &lt;region&gt; --sku Standard_LRS --kind StorageV2 --min-tls-version TLS1_2 --allow-blob-public-access false. Stage 1 checks that it exists.</t>
   </si>
   <si>
     <t>storage.access</t>
   </si>
   <si>
-    <t>BYO storage network access: privateEndpoint | serviceEndpoint (default privateEndpoint). Ignored when storage.model=managed.</t>
+    <t>Storage network access: privateEndpoint | serviceEndpoint (default privateEndpoint).</t>
   </si>
   <si>
     <t>SIZING &amp; SCALE</t>
@@ -1211,6 +1208,12 @@
   </si>
   <si>
     <t>Corp public ranges (intranet05..33)</t>
+  </si>
+  <si>
+    <t>byo-existing = use an existing, customer-prepared VNet and Discovery subnets; Stage 2 does NOT provision networking, and Stage 3 validates it. 
+byo = let Stage 2 provision the VNet, Discovery subnets and network controls using your supplied settings. 
+byo-spoke = use the same provisioning path for a Discovery spoke connected to your enterprise hub; you must arrange hub peering and firewall/NVA egress separately. 
+Both byo and byo-spoke can modify an existing VNet; they are not validation-only modes. FR1.2</t>
   </si>
 </sst>
 </file>
@@ -1439,15 +1442,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1751,7 +1754,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1760,7 +1763,7 @@
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.45" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1768,7 +1771,7 @@
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
@@ -1776,7 +1779,7 @@
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
     </row>
-    <row r="4" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -1791,7 +1794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>6</v>
       </c>
@@ -1800,7 +1803,7 @@
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
@@ -1811,7 +1814,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="25.75" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -1822,7 +1825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="36" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" ht="48" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>13</v>
       </c>
@@ -1833,7 +1836,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>16</v>
       </c>
@@ -1844,7 +1847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>19</v>
       </c>
@@ -1855,7 +1858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>22</v>
       </c>
@@ -1866,7 +1869,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="48" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" ht="48" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
@@ -1877,7 +1880,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>26</v>
       </c>
@@ -1888,7 +1891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="25.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>29</v>
       </c>
@@ -1899,7 +1902,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="51.45" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>32</v>
       </c>
@@ -1910,7 +1913,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>35</v>
       </c>
@@ -1919,7 +1922,7 @@
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
     </row>
-    <row r="18" spans="1:5" ht="24" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>36</v>
       </c>
@@ -1927,472 +1930,472 @@
         <v>37</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="E19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="12" t="s">
+    </row>
+    <row r="20" spans="1:5" ht="36" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="36" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="E20" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="12" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A21" s="10" t="s">
+      <c r="B21" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="E21" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="12" t="s">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A22" s="10" t="s">
+      <c r="B22" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="12" t="s">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A23" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="B23" s="11"/>
       <c r="E23" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A24" s="10" t="s">
+      <c r="B24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="12" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="24" x14ac:dyDescent="0.4">
-      <c r="A25" s="10" t="s">
+      <c r="B25" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="E25" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="12" t="s">
+    </row>
+    <row r="26" spans="1:5" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="24" x14ac:dyDescent="0.4">
-      <c r="A26" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="B26" s="11"/>
       <c r="E26" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A28" s="16" t="s">
-        <v>60</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="E29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E29" s="11" t="s">
+    </row>
+    <row r="30" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="D30" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="C31" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A31" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A32" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="11" t="s">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A34" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A35" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="11" t="s">
+      <c r="E35" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" s="11" t="s">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A37" s="16" t="s">
-        <v>81</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
       <c r="E37" s="15"/>
     </row>
-    <row r="38" spans="1:5" ht="24" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="E38" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E38" s="12" t="s">
+    </row>
+    <row r="39" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="24" x14ac:dyDescent="0.4">
-      <c r="A39" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="B39" s="11"/>
       <c r="E39" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="24" x14ac:dyDescent="0.4">
-      <c r="A40" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="B40" s="11"/>
       <c r="E40" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A42" s="16" t="s">
-        <v>89</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
       <c r="E42" s="15"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="E43" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E43" s="12" t="s">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A44" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>30</v>
       </c>
       <c r="E44" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A45" s="10" t="s">
+      <c r="B45" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="E45" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="E45" s="12" t="s">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A46" s="10" t="s">
+      <c r="B46" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="E46" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E46" s="12" t="s">
+    </row>
+    <row r="47" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="10" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="24" x14ac:dyDescent="0.4">
-      <c r="A47" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="B47" s="11"/>
       <c r="E47" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="24" x14ac:dyDescent="0.4">
-      <c r="A48" s="10" t="s">
+      <c r="B48" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="E48" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="E48" s="12" t="s">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A49" s="16" t="s">
-        <v>106</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="E50" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="E50" s="12" t="s">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A51" s="10" t="s">
+      <c r="B51" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="E51" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="E51" s="12" t="s">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A52" s="10" t="s">
+      <c r="B52" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="E52" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="E52" s="12" t="s">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A53" s="10" t="s">
+      <c r="B53" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="E53" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E53" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A54" s="10" t="s">
+      <c r="B54" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="E54" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="E54" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A55" s="10" t="s">
+      <c r="B55" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="E55" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E55" s="12" t="s">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A56" s="10" t="s">
+      <c r="B56" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="E56" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E56" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A57" s="10" t="s">
+      <c r="B57" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="E57" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="24" x14ac:dyDescent="0.4">
-      <c r="A58" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="B58" s="11"/>
       <c r="E58" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="16" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A60" s="16" t="s">
-        <v>129</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
       <c r="D60" s="15"/>
       <c r="E60" s="15"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B61" s="11"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B62" s="11"/>
       <c r="E62" s="12"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
       <c r="D64" s="15"/>
       <c r="E64" s="15"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
@@ -2411,7 +2414,7 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
-  <dataValidations count="10">
+  <dataValidations count="11">
     <dataValidation type="list" allowBlank="1" sqref="B9" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"devtest,prod"</formula1>
     </dataValidation>
@@ -2422,10 +2425,10 @@
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B18" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"managed,byo-existing,byo,byo-spoke,greenfield"</formula1>
+      <formula1>"byo,byo-spoke,byo-existing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B38" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>"byo,managed"</formula1>
+      <formula1>"byo"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E29 E30 E31 E32 E33 E34 E35" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"Microsoft.App/environments,Microsoft.ContainerService/managedClusters,none"</formula1>
@@ -2442,6 +2445,9 @@
     <dataValidation type="list" allowBlank="1" sqref="B48" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"Enabled,Disabled"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B25" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+      <formula1>"UserDefinedRouting,LoadBalancer"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
@@ -2451,140 +2457,140 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:C20"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="26.15" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="2" spans="2:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="15"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="15"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B3" s="18" t="s">
+      <c r="C3" s="15"/>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="15"/>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B10" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="16" spans="2:3" ht="16.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="16.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="3" t="s">
+    <row r="17" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="5" t="s">
+    </row>
+    <row r="18" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="5" t="s">
+    </row>
+    <row r="19" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C19" s="5" t="s">
+    </row>
+    <row r="20" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2599,11 +2605,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="23.15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" ht="23.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2613,9 +2619,9 @@
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -2637,7 +2643,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
@@ -2646,9 +2652,9 @@
     <col min="7" max="7" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
-        <v>163</v>
+    <row r="1" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>162</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2657,9 +2663,9 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -2668,12 +2674,12 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
     </row>
-    <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>165</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>166</v>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
@@ -2681,12 +2687,12 @@
       <c r="F4" s="23"/>
       <c r="G4" s="24"/>
     </row>
-    <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>147</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>148</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
@@ -2694,12 +2700,12 @@
       <c r="F5" s="23"/>
       <c r="G5" s="24"/>
     </row>
-    <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>167</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>168</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
@@ -2707,12 +2713,12 @@
       <c r="F6" s="23"/>
       <c r="G6" s="24"/>
     </row>
-    <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="22" t="s">
         <v>169</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>170</v>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -2720,12 +2726,12 @@
       <c r="F7" s="23"/>
       <c r="G7" s="24"/>
     </row>
-    <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>171</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>172</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -2733,12 +2739,12 @@
       <c r="F8" s="23"/>
       <c r="G8" s="24"/>
     </row>
-    <row r="9" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>173</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>174</v>
       </c>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -2746,9 +2752,9 @@
       <c r="F9" s="23"/>
       <c r="G9" s="24"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" s="25" t="s">
-        <v>175</v>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>174</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -2757,214 +2763,214 @@
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
     </row>
-    <row r="12" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:7" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
+      <c r="B14" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
+      <c r="B15" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="G15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:7" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+      <c r="C16" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="38.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="B17" s="6" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="38.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
+      <c r="C17" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="6" t="s">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G18" s="6" t="s">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
+      <c r="B19" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G19" s="6" t="s">
+    </row>
+    <row r="20" spans="1:7" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2973,7 +2979,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -2982,7 +2988,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -2991,7 +2997,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -3000,7 +3006,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -3009,7 +3015,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -3042,7 +3048,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -3053,9 +3059,9 @@
     <col min="8" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
-        <v>216</v>
+    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>215</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3065,9 +3071,9 @@
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -3077,241 +3083,241 @@
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
     </row>
-    <row r="4" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>222</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>223</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="H5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="F11" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -3321,7 +3327,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -3331,7 +3337,7 @@
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -3341,7 +3347,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -3351,7 +3357,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -3361,7 +3367,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -3388,7 +3394,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3399,9 +3405,9 @@
     <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
-        <v>272</v>
+    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>271</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3411,9 +3417,9 @@
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -3423,9 +3429,9 @@
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" s="25" t="s">
-        <v>183</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>182</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -3435,49 +3441,49 @@
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>276</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>277</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F6" s="6" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>281</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="25" t="s">
-        <v>282</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -3487,215 +3493,215 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>288</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>289</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="C10" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="F10" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="B11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="G11" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H11" s="6" t="s">
+      <c r="B12" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="F12" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="B13" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="B14" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:8" ht="38.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="38.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="F15" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="38.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="B16" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="38.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3705,7 +3711,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -3715,7 +3721,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -3725,7 +3731,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -3735,7 +3741,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -3759,7 +3765,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L74"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -3774,9 +3780,9 @@
     <col min="11" max="11" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
-        <v>311</v>
+    <row r="1" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>310</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3790,9 +3796,9 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -3806,2489 +3812,2489 @@
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
     </row>
-    <row r="4" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="K4" s="7" t="s">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>320</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>321</v>
       </c>
       <c r="C5" s="6">
         <v>100</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:12" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C6" s="6">
         <v>105</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C7" s="6">
         <v>65000</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C8" s="6">
         <v>65001</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>333</v>
-      </c>
       <c r="F8" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="K8" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C9" s="6">
         <v>65500</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="C10" s="6">
         <v>100</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J10" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K10" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:12" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C11" s="6">
         <v>105</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C12" s="6">
         <v>65000</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C13" s="6">
         <v>65001</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="H13" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="K13" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C14" s="6">
         <v>65500</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C15" s="6">
         <v>100</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J15" s="6" t="s">
+      <c r="K15" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:12" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C16" s="6">
         <v>105</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K16" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C17" s="6">
         <v>65000</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K17" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C18" s="6">
         <v>65001</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>333</v>
-      </c>
       <c r="F18" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="K18" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C19" s="6">
         <v>65500</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J19" s="6" t="s">
+      <c r="K19" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="C20" s="6">
         <v>100</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F20" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J20" s="6" t="s">
+      <c r="K20" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K20" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C21" s="6">
         <v>105</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K21" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C22" s="6">
         <v>65000</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C23" s="6">
         <v>65001</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="H23" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G23" s="6" t="s">
+      <c r="K23" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C24" s="6">
         <v>65500</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C25" s="6">
         <v>100</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F25" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J25" s="6" t="s">
+      <c r="K25" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C26" s="6">
         <v>105</v>
       </c>
       <c r="D26" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K26" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C27" s="6">
         <v>65000</v>
       </c>
       <c r="D27" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="F27" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K27" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C28" s="6">
         <v>65001</v>
       </c>
       <c r="D28" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>333</v>
-      </c>
       <c r="F28" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J28" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="K28" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C29" s="6">
         <v>65500</v>
       </c>
       <c r="D29" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J29" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J29" s="6" t="s">
+      <c r="K29" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A30" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="C30" s="6">
         <v>100</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F30" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J30" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J30" s="6" t="s">
+      <c r="K30" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C31" s="6">
         <v>105</v>
       </c>
       <c r="D31" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K31" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C32" s="6">
         <v>65000</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K32" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C33" s="6">
         <v>65001</v>
       </c>
       <c r="D33" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G33" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="H33" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G33" s="6" t="s">
+      <c r="K33" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C34" s="6">
         <v>65500</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C35" s="6">
         <v>100</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F35" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J35" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J35" s="6" t="s">
+      <c r="K35" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K35" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C36" s="6">
         <v>105</v>
       </c>
       <c r="D36" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K36" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C37" s="6">
         <v>65000</v>
       </c>
       <c r="D37" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="F37" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K37" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C38" s="6">
         <v>65001</v>
       </c>
       <c r="D38" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>333</v>
-      </c>
       <c r="F38" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="K38" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C39" s="6">
         <v>65500</v>
       </c>
       <c r="D39" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J39" s="6" t="s">
+      <c r="K39" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A40" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="C40" s="6">
         <v>100</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F40" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J40" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J40" s="6" t="s">
+      <c r="K40" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C41" s="6">
         <v>105</v>
       </c>
       <c r="D41" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K41" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C42" s="6">
         <v>65000</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K42" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C43" s="6">
         <v>65001</v>
       </c>
       <c r="D43" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G43" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="H43" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G43" s="6" t="s">
+      <c r="K43" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C44" s="6">
         <v>65500</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C45" s="6">
         <v>100</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F45" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J45" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J45" s="6" t="s">
+      <c r="K45" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K45" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C46" s="6">
         <v>105</v>
       </c>
       <c r="D46" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K46" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C47" s="6">
         <v>65000</v>
       </c>
       <c r="D47" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="F47" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K47" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F47" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C48" s="6">
         <v>65001</v>
       </c>
       <c r="D48" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>333</v>
-      </c>
       <c r="F48" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J48" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="K48" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C49" s="6">
         <v>65500</v>
       </c>
       <c r="D49" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J49" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J49" s="6" t="s">
+      <c r="K49" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="K49" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A50" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="C50" s="6">
         <v>100</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F50" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J50" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J50" s="6" t="s">
+      <c r="K50" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K50" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C51" s="6">
         <v>105</v>
       </c>
       <c r="D51" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K51" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C52" s="6">
         <v>65000</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K52" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C53" s="6">
         <v>65001</v>
       </c>
       <c r="D53" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G53" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="H53" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J53" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G53" s="6" t="s">
+      <c r="K53" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H53" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K53" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C54" s="6">
         <v>65500</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C55" s="6">
         <v>100</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F55" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J55" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J55" s="6" t="s">
+      <c r="K55" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C56" s="6">
         <v>105</v>
       </c>
       <c r="D56" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="F56" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K56" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C57" s="6">
         <v>65000</v>
       </c>
       <c r="D57" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="F57" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K57" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F57" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K57" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C58" s="6">
         <v>65001</v>
       </c>
       <c r="D58" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>333</v>
-      </c>
       <c r="F58" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J58" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="K58" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C59" s="6">
         <v>65500</v>
       </c>
       <c r="D59" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J59" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J59" s="6" t="s">
+      <c r="K59" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A60" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="C60" s="6">
         <v>100</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F60" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J60" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J60" s="6" t="s">
+      <c r="K60" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K60" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C61" s="6">
         <v>105</v>
       </c>
       <c r="D61" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K61" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J61" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K61" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C62" s="6">
         <v>65000</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K62" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J62" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C63" s="6">
         <v>65001</v>
       </c>
       <c r="D63" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G63" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="H63" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J63" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F63" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G63" s="6" t="s">
+      <c r="K63" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H63" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K63" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C64" s="6">
         <v>65500</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C65" s="6">
         <v>100</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F65" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J65" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G65" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J65" s="6" t="s">
+      <c r="K65" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K65" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C66" s="6">
         <v>105</v>
       </c>
       <c r="D66" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="F66" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K66" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K66" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C67" s="6">
         <v>65000</v>
       </c>
       <c r="D67" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E67" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="F67" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K67" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F67" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J67" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K67" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C68" s="6">
         <v>65001</v>
       </c>
       <c r="D68" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>333</v>
-      </c>
       <c r="F68" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J68" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G68" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J68" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="K68" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C69" s="6">
         <v>65500</v>
       </c>
       <c r="D69" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J69" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J69" s="6" t="s">
+      <c r="K69" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="K69" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A70" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="C70" s="6">
         <v>100</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F70" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J70" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G70" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J70" s="6" t="s">
+      <c r="K70" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="K70" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="25.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C71" s="6">
         <v>105</v>
       </c>
       <c r="D71" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K71" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J71" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K71" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C72" s="6">
         <v>65000</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="K72" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J72" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C73" s="6">
         <v>65001</v>
       </c>
       <c r="D73" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G73" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E73" s="6" t="s">
+      <c r="H73" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="J73" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F73" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G73" s="6" t="s">
+      <c r="K73" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="H73" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J73" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="K73" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C74" s="6">
         <v>65500</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -6314,7 +6320,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -6322,9 +6328,9 @@
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
-        <v>345</v>
+    <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>344</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6332,9 +6338,9 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -6342,9 +6348,9 @@
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A4" s="25" t="s">
-        <v>347</v>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>346</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -6352,300 +6358,300 @@
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
     </row>
-    <row r="5" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>350</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>351</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="E7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
+      <c r="B9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B11" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
+      <c r="B12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B13" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
+      <c r="B14" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B15" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
+      <c r="B17" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E17" s="6" t="s">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
+      <c r="B19" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
